--- a/Zinc/5. Cluster analysis/Clustering by sample results/Site_typology_sample_counts.xlsx
+++ b/Zinc/5. Cluster analysis/Clustering by sample results/Site_typology_sample_counts.xlsx
@@ -1,148 +1,155 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <workbookPr date1904="false"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://irtacat-my.sharepoint.com/personal/cecilia_albert_irta_cat/Documents/Escriptori/Trace-element-bioavailability-spatial-assessment/Zinc/5. Cluster analysis/Clustering by sample results/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_C232D23C0059E8E15F255F3B513D01FEC2DBBEDB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C84D4596-9970-40F0-8FB0-3626C30BA1AD}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sites" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sites" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
-  <si>
-    <t xml:space="preserve">Site</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Typology</t>
-  </si>
-  <si>
-    <t xml:space="preserve">n_samples</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BCK0.9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Main Stem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Developed Perennial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Perennial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BSL1.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BSL1.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BSL2.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BSL2.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BSL3.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BSL3.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BSL3.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BSL4.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pooled</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BSL4.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BSL4.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Downtown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EFK10.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EFK13.8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EFK16.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EFK18.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EFK2.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EFK20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EFK5.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EFK7.9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MCA1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MCA3.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MCA3.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Non-Perennial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MCA4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MTN1.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MTN4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NBO2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NBO3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NBO5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pinhook Branch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WBK1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WBK2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WBK3</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="41">
+  <si>
+    <t>Site</t>
+  </si>
+  <si>
+    <t>Typology</t>
+  </si>
+  <si>
+    <t>n_samples</t>
+  </si>
+  <si>
+    <t>BCK0.9</t>
+  </si>
+  <si>
+    <t>Main Stem</t>
+  </si>
+  <si>
+    <t>Developed Perennial</t>
+  </si>
+  <si>
+    <t>Perennial</t>
+  </si>
+  <si>
+    <t>BSL1.1</t>
+  </si>
+  <si>
+    <t>BSL1.3</t>
+  </si>
+  <si>
+    <t>BSL2.2</t>
+  </si>
+  <si>
+    <t>BSL2.3</t>
+  </si>
+  <si>
+    <t>BSL3.1</t>
+  </si>
+  <si>
+    <t>BSL3.2</t>
+  </si>
+  <si>
+    <t>BSL3.3</t>
+  </si>
+  <si>
+    <t>BSL4.1</t>
+  </si>
+  <si>
+    <t>Pooled</t>
+  </si>
+  <si>
+    <t>BSL4.2</t>
+  </si>
+  <si>
+    <t>BSL4.3</t>
+  </si>
+  <si>
+    <t>Downtown</t>
+  </si>
+  <si>
+    <t>EFK10.0</t>
+  </si>
+  <si>
+    <t>EFK13.8</t>
+  </si>
+  <si>
+    <t>EFK16.2</t>
+  </si>
+  <si>
+    <t>EFK18.2</t>
+  </si>
+  <si>
+    <t>EFK2.0</t>
+  </si>
+  <si>
+    <t>EFK20</t>
+  </si>
+  <si>
+    <t>EFK5.4</t>
+  </si>
+  <si>
+    <t>EFK7.9</t>
+  </si>
+  <si>
+    <t>MCA1</t>
+  </si>
+  <si>
+    <t>MCA3.1</t>
+  </si>
+  <si>
+    <t>MCA3.2</t>
+  </si>
+  <si>
+    <t>Non-Perennial</t>
+  </si>
+  <si>
+    <t>MCA4</t>
+  </si>
+  <si>
+    <t>MTN1.1</t>
+  </si>
+  <si>
+    <t>MTN4</t>
+  </si>
+  <si>
+    <t>NBO2</t>
+  </si>
+  <si>
+    <t>NBO3</t>
+  </si>
+  <si>
+    <t>NBO5</t>
+  </si>
+  <si>
+    <t>Pinhook Branch</t>
+  </si>
+  <si>
+    <t>WBK1</t>
+  </si>
+  <si>
+    <t>WBK2</t>
+  </si>
+  <si>
+    <t>WBK3</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -178,6 +185,15 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -459,11 +475,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:C75"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="13.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.08984375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -474,822 +494,822 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
         <v>4</v>
       </c>
-      <c r="C2" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3">
+      <c r="C2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3" t="s">
         <v>5</v>
       </c>
-      <c r="C3" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4">
+      <c r="C3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="B4" t="s">
         <v>6</v>
       </c>
-      <c r="C4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5">
+      <c r="C4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>7</v>
       </c>
       <c r="B5" t="s">
         <v>5</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5">
         <v>8</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>7</v>
       </c>
       <c r="B6" t="s">
         <v>4</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6">
         <v>3</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>8</v>
       </c>
       <c r="B7" t="s">
         <v>5</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7">
         <v>9</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>8</v>
       </c>
       <c r="B8" t="s">
         <v>6</v>
       </c>
-      <c r="C8" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9">
+      <c r="C8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>8</v>
       </c>
       <c r="B9" t="s">
         <v>4</v>
       </c>
-      <c r="C9" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10">
+      <c r="C9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>9</v>
       </c>
       <c r="B10" t="s">
         <v>5</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C10">
         <v>8</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>9</v>
       </c>
       <c r="B11" t="s">
         <v>6</v>
       </c>
-      <c r="C11" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12">
+      <c r="C11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>9</v>
       </c>
       <c r="B12" t="s">
         <v>4</v>
       </c>
-      <c r="C12" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13">
+      <c r="C12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>10</v>
       </c>
       <c r="B13" t="s">
         <v>5</v>
       </c>
-      <c r="C13" t="n">
+      <c r="C13">
         <v>9</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>10</v>
       </c>
       <c r="B14" t="s">
         <v>6</v>
       </c>
-      <c r="C14" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15">
+      <c r="C14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>11</v>
       </c>
       <c r="B15" t="s">
         <v>5</v>
       </c>
-      <c r="C15" t="n">
+      <c r="C15">
         <v>10</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>11</v>
       </c>
       <c r="B16" t="s">
         <v>6</v>
       </c>
-      <c r="C16" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17">
+      <c r="C16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>12</v>
       </c>
       <c r="B17" t="s">
         <v>5</v>
       </c>
-      <c r="C17" t="n">
+      <c r="C17">
         <v>10</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>12</v>
       </c>
       <c r="B18" t="s">
         <v>4</v>
       </c>
-      <c r="C18" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19">
+      <c r="C18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>13</v>
       </c>
       <c r="B19" t="s">
         <v>5</v>
       </c>
-      <c r="C19" t="n">
+      <c r="C19">
         <v>9</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>13</v>
       </c>
       <c r="B20" t="s">
         <v>4</v>
       </c>
-      <c r="C20" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21">
+      <c r="C20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>14</v>
       </c>
       <c r="B21" t="s">
         <v>15</v>
       </c>
-      <c r="C21" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22">
+      <c r="C21">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>14</v>
       </c>
       <c r="B22" t="s">
         <v>6</v>
       </c>
-      <c r="C22" t="n">
+      <c r="C22">
         <v>2</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>16</v>
       </c>
       <c r="B23" t="s">
         <v>15</v>
       </c>
-      <c r="C23" t="n">
+      <c r="C23">
         <v>3</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>16</v>
       </c>
       <c r="B24" t="s">
         <v>6</v>
       </c>
-      <c r="C24" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25">
+      <c r="C24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>17</v>
       </c>
       <c r="B25" t="s">
         <v>15</v>
       </c>
-      <c r="C25" t="n">
+      <c r="C25">
         <v>3</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>17</v>
       </c>
       <c r="B26" t="s">
         <v>6</v>
       </c>
-      <c r="C26" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27">
+      <c r="C26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>18</v>
       </c>
       <c r="B27" t="s">
         <v>5</v>
       </c>
-      <c r="C27" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="28">
+      <c r="C27">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>18</v>
       </c>
       <c r="B28" t="s">
         <v>4</v>
       </c>
-      <c r="C28" t="n">
+      <c r="C28">
         <v>3</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>18</v>
       </c>
       <c r="B29" t="s">
         <v>6</v>
       </c>
-      <c r="C29" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30">
+      <c r="C29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>19</v>
       </c>
       <c r="B30" t="s">
         <v>4</v>
       </c>
-      <c r="C30" t="n">
+      <c r="C30">
         <v>10</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>19</v>
       </c>
       <c r="B31" t="s">
         <v>6</v>
       </c>
-      <c r="C31" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32">
+      <c r="C31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>20</v>
       </c>
       <c r="B32" t="s">
         <v>4</v>
       </c>
-      <c r="C32" t="n">
+      <c r="C32">
         <v>9</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>20</v>
       </c>
       <c r="B33" t="s">
         <v>6</v>
       </c>
-      <c r="C33" t="n">
+      <c r="C33">
         <v>2</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>21</v>
       </c>
       <c r="B34" t="s">
         <v>4</v>
       </c>
-      <c r="C34" t="n">
+      <c r="C34">
         <v>10</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>21</v>
       </c>
       <c r="B35" t="s">
         <v>6</v>
       </c>
-      <c r="C35" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36">
+      <c r="C35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>22</v>
       </c>
       <c r="B36" t="s">
         <v>4</v>
       </c>
-      <c r="C36" t="n">
+      <c r="C36">
         <v>9</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>22</v>
       </c>
       <c r="B37" t="s">
         <v>6</v>
       </c>
-      <c r="C37" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38">
+      <c r="C37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>23</v>
       </c>
       <c r="B38" t="s">
         <v>4</v>
       </c>
-      <c r="C38" t="n">
+      <c r="C38">
         <v>10</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>23</v>
       </c>
       <c r="B39" t="s">
         <v>6</v>
       </c>
-      <c r="C39" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40">
+      <c r="C39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>24</v>
       </c>
       <c r="B40" t="s">
         <v>4</v>
       </c>
-      <c r="C40" t="n">
+      <c r="C40">
         <v>9</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>24</v>
       </c>
       <c r="B41" t="s">
         <v>6</v>
       </c>
-      <c r="C41" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42">
+      <c r="C41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>25</v>
       </c>
       <c r="B42" t="s">
         <v>4</v>
       </c>
-      <c r="C42" t="n">
+      <c r="C42">
         <v>10</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>25</v>
       </c>
       <c r="B43" t="s">
         <v>6</v>
       </c>
-      <c r="C43" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44">
+      <c r="C43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>26</v>
       </c>
       <c r="B44" t="s">
         <v>4</v>
       </c>
-      <c r="C44" t="n">
+      <c r="C44">
         <v>8</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>26</v>
       </c>
       <c r="B45" t="s">
         <v>6</v>
       </c>
-      <c r="C45" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46">
+      <c r="C45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>27</v>
       </c>
       <c r="B46" t="s">
         <v>5</v>
       </c>
-      <c r="C46" t="n">
+      <c r="C46">
         <v>8</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>27</v>
       </c>
       <c r="B47" t="s">
         <v>6</v>
       </c>
-      <c r="C47" t="n">
+      <c r="C47">
         <v>3</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>28</v>
       </c>
       <c r="B48" t="s">
         <v>6</v>
       </c>
-      <c r="C48" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="49">
+      <c r="C48">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>28</v>
       </c>
       <c r="B49" t="s">
         <v>5</v>
       </c>
-      <c r="C49" t="n">
+      <c r="C49">
         <v>3</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>28</v>
       </c>
       <c r="B50" t="s">
         <v>15</v>
       </c>
-      <c r="C50" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51">
+      <c r="C50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>29</v>
       </c>
       <c r="B51" t="s">
         <v>30</v>
       </c>
-      <c r="C51" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="52">
+      <c r="C51">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>29</v>
       </c>
       <c r="B52" t="s">
         <v>15</v>
       </c>
-      <c r="C52" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="53">
+      <c r="C52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>31</v>
       </c>
       <c r="B53" t="s">
         <v>6</v>
       </c>
-      <c r="C53" t="n">
+      <c r="C53">
         <v>8</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>31</v>
       </c>
       <c r="B54" t="s">
         <v>5</v>
       </c>
-      <c r="C54" t="n">
+      <c r="C54">
         <v>3</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>32</v>
       </c>
       <c r="B55" t="s">
         <v>15</v>
       </c>
-      <c r="C55" t="n">
+      <c r="C55">
         <v>8</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>32</v>
       </c>
       <c r="B56" t="s">
         <v>5</v>
       </c>
-      <c r="C56" t="n">
+      <c r="C56">
         <v>2</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>33</v>
       </c>
       <c r="B57" t="s">
         <v>6</v>
       </c>
-      <c r="C57" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="58">
+      <c r="C57">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>33</v>
       </c>
       <c r="B58" t="s">
         <v>5</v>
       </c>
-      <c r="C58" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="59">
+      <c r="C58">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>33</v>
       </c>
       <c r="B59" t="s">
         <v>30</v>
       </c>
-      <c r="C59" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="60">
+      <c r="C59">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>34</v>
       </c>
       <c r="B60" t="s">
         <v>5</v>
       </c>
-      <c r="C60" t="n">
+      <c r="C60">
         <v>8</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>34</v>
       </c>
       <c r="B61" t="s">
         <v>4</v>
       </c>
-      <c r="C61" t="n">
+      <c r="C61">
         <v>2</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>34</v>
       </c>
       <c r="B62" t="s">
         <v>6</v>
       </c>
-      <c r="C62" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="63">
+      <c r="C62">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>35</v>
       </c>
       <c r="B63" t="s">
         <v>30</v>
       </c>
-      <c r="C63" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="64">
+      <c r="C63">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>35</v>
       </c>
       <c r="B64" t="s">
         <v>6</v>
       </c>
-      <c r="C64" t="n">
+      <c r="C64">
         <v>2</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>36</v>
       </c>
       <c r="B65" t="s">
         <v>6</v>
       </c>
-      <c r="C65" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="66">
+      <c r="C65">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>36</v>
       </c>
       <c r="B66" t="s">
         <v>15</v>
       </c>
-      <c r="C66" t="n">
+      <c r="C66">
         <v>2</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>37</v>
       </c>
       <c r="B67" t="s">
         <v>6</v>
       </c>
-      <c r="C67" t="n">
+      <c r="C67">
         <v>9</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>37</v>
       </c>
       <c r="B68" t="s">
         <v>4</v>
       </c>
-      <c r="C68" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="69">
+      <c r="C68">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>38</v>
       </c>
       <c r="B69" t="s">
         <v>5</v>
       </c>
-      <c r="C69" t="n">
+      <c r="C69">
         <v>11</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>38</v>
       </c>
       <c r="B70" t="s">
         <v>6</v>
       </c>
-      <c r="C70" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="71">
+      <c r="C70">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>39</v>
       </c>
       <c r="B71" t="s">
         <v>6</v>
       </c>
-      <c r="C71" t="n">
+      <c r="C71">
         <v>2</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>39</v>
       </c>
       <c r="B72" t="s">
         <v>15</v>
       </c>
-      <c r="C72" t="n">
+      <c r="C72">
         <v>2</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>39</v>
       </c>
       <c r="B73" t="s">
         <v>30</v>
       </c>
-      <c r="C73" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="74">
+      <c r="C73">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>40</v>
       </c>
       <c r="B74" t="s">
         <v>6</v>
       </c>
-      <c r="C74" t="n">
+      <c r="C74">
         <v>7</v>
       </c>
     </row>
-    <row r="75">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>40</v>
       </c>
       <c r="B75" t="s">
         <v>15</v>
       </c>
-      <c r="C75" t="n">
+      <c r="C75">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>